--- a/output/指数回撤分析结果_20251201.xlsx
+++ b/output/指数回撤分析结果_20251201.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="日经225_回撤分析" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="德国dax_回撤分析" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="英国富时100_回撤分析" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,16 +464,16 @@
         <v>2000</v>
       </c>
       <c r="B2" t="n">
-        <v>-35.56821056380654</v>
+        <v>-11.03954886102248</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>36628</v>
+        <v>36609</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>36881</v>
+        <v>36633</v>
       </c>
       <c r="E2" t="n">
-        <v>253</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -482,16 +481,16 @@
         <v>2001</v>
       </c>
       <c r="B3" t="n">
-        <v>-33.48466133157908</v>
+        <v>-29.55000476689865</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>37019</v>
+        <v>36928</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>37151</v>
+        <v>37155</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
@@ -499,16 +498,16 @@
         <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>-30.68869810556894</v>
+        <v>-31.04361546263947</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>37399</v>
+        <v>37260</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>37574</v>
+        <v>37523</v>
       </c>
       <c r="E4" t="n">
-        <v>175</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
@@ -516,16 +515,16 @@
         <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>-13.86086898871229</v>
+        <v>-18.01970320488839</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>37914</v>
+        <v>37623</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>37944</v>
+        <v>37692</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -533,16 +532,16 @@
         <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>-13.63741368920633</v>
+        <v>-6.30941713836134</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>38103</v>
+        <v>38104</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>38124</v>
+        <v>38194</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -550,16 +549,16 @@
         <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>-9.537307308871551</v>
+        <v>-6.41879595253694</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>38420</v>
+        <v>38623</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>38489</v>
+        <v>38646</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -567,16 +566,16 @@
         <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>-19.04401034653372</v>
+        <v>-10.20594517912175</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>38814</v>
+        <v>38828</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>38881</v>
+        <v>38882</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -584,16 +583,16 @@
         <v>2007</v>
       </c>
       <c r="B9" t="n">
-        <v>-18.75108832667652</v>
+        <v>-12.97457073257679</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>39272</v>
+        <v>39248</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>39407</v>
+        <v>39310</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -601,16 +600,16 @@
         <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>-53.20745398744953</v>
+        <v>-41.64644874525419</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>39449</v>
+        <v>39450</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>39748</v>
+        <v>39773</v>
       </c>
       <c r="E10" t="n">
-        <v>299</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -618,16 +617,16 @@
         <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>-23.64112199704738</v>
+        <v>-24.29078319953782</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>39820</v>
+        <v>39819</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>39882</v>
+        <v>39875</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -635,16 +634,16 @@
         <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>-21.8613934682449</v>
+        <v>-17.49799571159535</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>40275</v>
+        <v>40283</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>40421</v>
+        <v>40360</v>
       </c>
       <c r="E12" t="n">
-        <v>146</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -652,16 +651,16 @@
         <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>-24.84469303791931</v>
+        <v>-17.74523686709225</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>40595</v>
+        <v>40591</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>40872</v>
+        <v>40765</v>
       </c>
       <c r="E13" t="n">
-        <v>277</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -669,16 +668,16 @@
         <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>-19.10766785468765</v>
+        <v>-11.8243322526896</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>40995</v>
+        <v>40984</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>41064</v>
+        <v>41061</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -686,16 +685,16 @@
         <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>-20.36108697238032</v>
+        <v>-11.85874241806245</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>41416</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>41438</v>
+        <v>41449</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -703,16 +702,16 @@
         <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>-14.61607445932832</v>
+        <v>-10.11515608803676</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>41641</v>
+        <v>41773</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>41743</v>
+        <v>41988</v>
       </c>
       <c r="E16" t="n">
-        <v>102</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17">
@@ -720,16 +719,16 @@
         <v>2015</v>
       </c>
       <c r="B17" t="n">
-        <v>-18.86708999364098</v>
+        <v>-17.31311180493187</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>42179</v>
+        <v>42121</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>42276</v>
+        <v>42352</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
@@ -737,16 +736,16 @@
         <v>2016</v>
       </c>
       <c r="B18" t="n">
-        <v>-18.9635455677693</v>
+        <v>-7.592983747929108</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>42373</v>
+        <v>42480</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>42545</v>
+        <v>42535</v>
       </c>
       <c r="E18" t="n">
-        <v>172</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -754,16 +753,16 @@
         <v>2017</v>
       </c>
       <c r="B19" t="n">
-        <v>-6.611676322658681</v>
+        <v>-4.400851658070147</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>42807</v>
+        <v>42881</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>42839</v>
+        <v>42993</v>
       </c>
       <c r="E19" t="n">
-        <v>32</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20">
@@ -771,16 +770,16 @@
         <v>2018</v>
       </c>
       <c r="B20" t="n">
-        <v>-20.58164082646629</v>
+        <v>-16.41102133304559</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>43371</v>
+        <v>43242</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>43459</v>
+        <v>43461</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21">
@@ -788,16 +787,16 @@
         <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>-9.174191014892699</v>
+        <v>-8.06077061279289</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>43580</v>
+        <v>43675</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>43703</v>
+        <v>43692</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -805,16 +804,16 @@
         <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>-31.26903013721836</v>
+        <v>-34.92929887837218</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>43850</v>
+        <v>43847</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>43909</v>
+        <v>43913</v>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
@@ -822,16 +821,16 @@
         <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>-10.65891786934091</v>
+        <v>-6.776987921306632</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>44245</v>
+        <v>44204</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>44428</v>
+        <v>44225</v>
       </c>
       <c r="E23" t="n">
-        <v>183</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -839,16 +838,16 @@
         <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>-15.73232247471718</v>
+        <v>-11.02979510974402</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>44566</v>
+        <v>44602</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>44629</v>
+        <v>44846</v>
       </c>
       <c r="E24" t="n">
-        <v>63</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25">
@@ -856,16 +855,16 @@
         <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>-9.33700467479802</v>
+        <v>-9.450220917334127</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>45110</v>
+        <v>44977</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45225</v>
+        <v>45114</v>
       </c>
       <c r="E25" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26">
@@ -873,16 +872,16 @@
         <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>-25.4963880748446</v>
+        <v>-5.180918326268675</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>45484</v>
+        <v>45427</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
@@ -890,499 +889,16 @@
         <v>2025</v>
       </c>
       <c r="B27" t="n">
-        <v>-22.32031793789433</v>
+        <v>-13.43465621199124</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45664</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>45754</v>
-      </c>
-      <c r="E27" t="n">
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>年份</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>最大回撤(%)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>回撤开始时间</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>回撤结束时间</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>持续天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-23.11552305836228</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>36592</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>36881</v>
-      </c>
-      <c r="E2" t="n">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-43.41531414023245</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>36928</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>37155</v>
-      </c>
-      <c r="E3" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B4" t="n">
-        <v>-52.4419913776533</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>37334</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="E4" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B5" t="n">
-        <v>-30.2253543431784</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>37627</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>37692</v>
-      </c>
-      <c r="E5" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B6" t="n">
-        <v>-12.0357260871348</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>38054</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>38212</v>
-      </c>
-      <c r="E6" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B7" t="n">
-        <v>-5.645549209704405</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>38418</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>38470</v>
-      </c>
-      <c r="E7" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B8" t="n">
-        <v>-13.81890071522557</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>38846</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>38881</v>
-      </c>
-      <c r="E8" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B9" t="n">
-        <v>-10.30905450368815</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>39279</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>39310</v>
-      </c>
-      <c r="E9" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B10" t="n">
-        <v>-48.07708032723161</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>39449</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>39773</v>
-      </c>
-      <c r="E10" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B11" t="n">
-        <v>-27.05563325779748</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>39819</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>39878</v>
-      </c>
-      <c r="E11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B12" t="n">
-        <v>-10.45561504082374</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>40294</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>40323</v>
-      </c>
-      <c r="E12" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B13" t="n">
-        <v>-31.27636583333999</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>40662</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>40808</v>
-      </c>
-      <c r="E13" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B14" t="n">
-        <v>-16.60309982648348</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>40984</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>41065</v>
-      </c>
-      <c r="E14" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B15" t="n">
-        <v>-9.828282863804359</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>41416</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>41449</v>
-      </c>
-      <c r="E15" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B16" t="n">
-        <v>-14.53203222914961</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>41823</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>41927</v>
-      </c>
-      <c r="E16" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B17" t="n">
-        <v>-23.81538829534059</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>42104</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>42271</v>
-      </c>
-      <c r="E17" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B18" t="n">
-        <v>-11.39649469937246</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>42374</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>42416</v>
-      </c>
-      <c r="E18" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B19" t="n">
-        <v>-7.316887721653055</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>42905</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>42976</v>
-      </c>
-      <c r="E19" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B20" t="n">
-        <v>-23.43793327236792</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>43123</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>43461</v>
-      </c>
-      <c r="E20" t="n">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B21" t="n">
-        <v>-9.637685175654594</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>43650</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>43692</v>
-      </c>
-      <c r="E21" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B22" t="n">
-        <v>-38.77938936833709</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>43908</v>
-      </c>
-      <c r="E22" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B23" t="n">
-        <v>-7.082584411053262</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>44517</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>44530</v>
-      </c>
-      <c r="E23" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B24" t="n">
-        <v>-26.40281469417857</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>44566</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>44833</v>
-      </c>
-      <c r="E24" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B25" t="n">
-        <v>-10.82190075744926</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>45135</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>45226</v>
-      </c>
-      <c r="E25" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B26" t="n">
-        <v>-8.110290969063076</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>45427</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>45509</v>
-      </c>
-      <c r="E26" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B27" t="n">
-        <v>-16.00633318929369</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>45722</v>
+        <v>45719</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>45756</v>
       </c>
       <c r="E27" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
